--- a/py project/battery/refactored_results/training_sets/battery_K_means_n180_r1.xlsx
+++ b/py project/battery/refactored_results/training_sets/battery_K_means_n180_r1.xlsx
@@ -8433,13 +8433,13 @@
         <v>45</v>
       </c>
       <c r="J182" t="n">
-        <v>-751.4</v>
+        <v>751.4</v>
       </c>
       <c r="K182" t="n">
-        <v>3.3091</v>
+        <v>3.3265</v>
       </c>
       <c r="L182" t="n">
-        <v>7.72325</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="183">
@@ -8474,16 +8474,16 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="J183" t="n">
-        <v>-2251.4</v>
+        <v>-401</v>
       </c>
       <c r="K183" t="n">
-        <v>3.2738</v>
+        <v>3.2998</v>
       </c>
       <c r="L183" t="n">
-        <v>34.75269444444444</v>
+        <v>16.22594444444444</v>
       </c>
     </row>
     <row r="184">
@@ -8518,16 +8518,16 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J184" t="n">
-        <v>-3002.2</v>
+        <v>-2251.4</v>
       </c>
       <c r="K184" t="n">
-        <v>3.2691</v>
+        <v>3.271</v>
       </c>
       <c r="L184" t="n">
-        <v>21.61525</v>
+        <v>37.87438888888889</v>
       </c>
     </row>
     <row r="185">
@@ -8562,16 +8562,16 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J185" t="n">
-        <v>-400.2</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>3.3203</v>
+        <v>3.3231</v>
       </c>
       <c r="L185" t="n">
-        <v>13.66244444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -8606,16 +8606,16 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J186" t="n">
-        <v>401.7</v>
+        <v>-750.7</v>
       </c>
       <c r="K186" t="n">
-        <v>3.332</v>
+        <v>3.3038</v>
       </c>
       <c r="L186" t="n">
-        <v>2.454444444444444</v>
+        <v>39.96538888888889</v>
       </c>
     </row>
     <row r="187">
@@ -8650,16 +8650,16 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="J187" t="n">
-        <v>-800.5</v>
+        <v>-3002.2</v>
       </c>
       <c r="K187" t="n">
-        <v>3.311</v>
+        <v>3.2325</v>
       </c>
       <c r="L187" t="n">
-        <v>11.43786111111111</v>
+        <v>24.12127777777778</v>
       </c>
     </row>
     <row r="188">
@@ -8694,16 +8694,16 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J188" t="n">
-        <v>376.4</v>
+        <v>1502.2</v>
       </c>
       <c r="K188" t="n">
-        <v>3.3333</v>
+        <v>3.332</v>
       </c>
       <c r="L188" t="n">
-        <v>0.8371388888888889</v>
+        <v>5.912666666666667</v>
       </c>
     </row>
     <row r="189">
@@ -8738,16 +8738,16 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>377.2</v>
       </c>
       <c r="K189" t="n">
-        <v>3.3277</v>
+        <v>3.3289</v>
       </c>
       <c r="L189" t="n">
-        <v>45.80002777777778</v>
+        <v>0.5240833333333333</v>
       </c>
     </row>
     <row r="190">
@@ -8829,13 +8829,13 @@
         <v>25</v>
       </c>
       <c r="J191" t="n">
-        <v>-3001.4</v>
+        <v>-802</v>
       </c>
       <c r="K191" t="n">
-        <v>3.2716</v>
+        <v>3.3088</v>
       </c>
       <c r="L191" t="n">
-        <v>19.1205</v>
+        <v>12.77888888888889</v>
       </c>
     </row>
     <row r="192">
@@ -8870,16 +8870,16 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J192" t="n">
-        <v>-750.7</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>3.3038</v>
+        <v>3.3085</v>
       </c>
       <c r="L192" t="n">
-        <v>8.352416666666667</v>
+        <v>45.81275</v>
       </c>
     </row>
     <row r="193">
@@ -8914,16 +8914,16 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J193" t="n">
-        <v>-2251.4</v>
+        <v>-400.2</v>
       </c>
       <c r="K193" t="n">
-        <v>3.271</v>
+        <v>3.3203</v>
       </c>
       <c r="L193" t="n">
-        <v>29.12347222222222</v>
+        <v>13.66244444444444</v>
       </c>
     </row>
     <row r="194">
@@ -8958,16 +8958,16 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J194" t="n">
-        <v>1502.2</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>3.3401</v>
+        <v>3.3277</v>
       </c>
       <c r="L194" t="n">
-        <v>7.577833333333333</v>
+        <v>45.80002777777778</v>
       </c>
     </row>
     <row r="195">
@@ -9005,13 +9005,13 @@
         <v>25</v>
       </c>
       <c r="J195" t="n">
-        <v>752.2</v>
+        <v>-401</v>
       </c>
       <c r="K195" t="n">
-        <v>3.3203</v>
+        <v>3.3165</v>
       </c>
       <c r="L195" t="n">
-        <v>4.240583333333333</v>
+        <v>10.66263888888889</v>
       </c>
     </row>
     <row r="196">
@@ -9046,16 +9046,16 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J196" t="n">
-        <v>-802</v>
+        <v>-751.4</v>
       </c>
       <c r="K196" t="n">
-        <v>3.3088</v>
+        <v>3.3091</v>
       </c>
       <c r="L196" t="n">
-        <v>11.66311111111111</v>
+        <v>42.67052777777778</v>
       </c>
     </row>
     <row r="197">
@@ -9090,16 +9090,16 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J197" t="n">
-        <v>-401</v>
+        <v>-751.4</v>
       </c>
       <c r="K197" t="n">
-        <v>3.3165</v>
+        <v>3.28</v>
       </c>
       <c r="L197" t="n">
-        <v>9.325333333333333</v>
+        <v>45.39533333333333</v>
       </c>
     </row>
     <row r="198">
@@ -9134,16 +9134,16 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J198" t="n">
-        <v>0</v>
+        <v>-375.7</v>
       </c>
       <c r="K198" t="n">
-        <v>3.3231</v>
+        <v>3.302</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>5.637666666666667</v>
       </c>
     </row>
     <row r="199">
@@ -9181,13 +9181,13 @@
         <v>25</v>
       </c>
       <c r="J199" t="n">
-        <v>-375.7</v>
+        <v>402.5</v>
       </c>
       <c r="K199" t="n">
-        <v>3.32</v>
+        <v>3.3271</v>
       </c>
       <c r="L199" t="n">
-        <v>4.489611111111111</v>
+        <v>2.012222222222222</v>
       </c>
     </row>
     <row r="200">
@@ -9225,13 +9225,13 @@
         <v>25</v>
       </c>
       <c r="J200" t="n">
-        <v>377.2</v>
+        <v>-375.7</v>
       </c>
       <c r="K200" t="n">
-        <v>3.3289</v>
+        <v>3.32</v>
       </c>
       <c r="L200" t="n">
-        <v>0.5240833333333333</v>
+        <v>4.489611111111111</v>
       </c>
     </row>
     <row r="201">
@@ -9266,16 +9266,16 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J201" t="n">
-        <v>0</v>
+        <v>-3001.4</v>
       </c>
       <c r="K201" t="n">
-        <v>3.3085</v>
+        <v>3.2703</v>
       </c>
       <c r="L201" t="n">
-        <v>8.769805555555555</v>
+        <v>18.27588888888889</v>
       </c>
     </row>
     <row r="202">
@@ -9310,16 +9310,16 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J202" t="n">
-        <v>751.4</v>
+        <v>-2251.4</v>
       </c>
       <c r="K202" t="n">
-        <v>3.2979</v>
+        <v>3.2738</v>
       </c>
       <c r="L202" t="n">
-        <v>3.400638888888889</v>
+        <v>34.75269444444444</v>
       </c>
     </row>
     <row r="203">
@@ -9357,13 +9357,13 @@
         <v>5</v>
       </c>
       <c r="J203" t="n">
-        <v>376.4</v>
+        <v>752.2</v>
       </c>
       <c r="K203" t="n">
-        <v>3.3153</v>
+        <v>3.3063</v>
       </c>
       <c r="L203" t="n">
-        <v>0.6277777777777778</v>
+        <v>4.236</v>
       </c>
     </row>
     <row r="204">
@@ -9398,16 +9398,16 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J204" t="n">
-        <v>1502.2</v>
+        <v>376.4</v>
       </c>
       <c r="K204" t="n">
-        <v>3.3289</v>
+        <v>3.3333</v>
       </c>
       <c r="L204" t="n">
-        <v>5.487805555555555</v>
+        <v>0.8371388888888889</v>
       </c>
     </row>
     <row r="205">
@@ -9445,13 +9445,13 @@
         <v>5</v>
       </c>
       <c r="J205" t="n">
-        <v>-401</v>
+        <v>-2252.2</v>
       </c>
       <c r="K205" t="n">
-        <v>3.2998</v>
+        <v>3.2325</v>
       </c>
       <c r="L205" t="n">
-        <v>15.44636111111111</v>
+        <v>37.88330555555556</v>
       </c>
     </row>
     <row r="206">
@@ -9489,13 +9489,13 @@
         <v>5</v>
       </c>
       <c r="J206" t="n">
-        <v>-2252.2</v>
+        <v>376.4</v>
       </c>
       <c r="K206" t="n">
-        <v>3.2325</v>
+        <v>3.3153</v>
       </c>
       <c r="L206" t="n">
-        <v>37.88330555555556</v>
+        <v>0.6277777777777778</v>
       </c>
     </row>
     <row r="207">
@@ -9574,16 +9574,16 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J208" t="n">
-        <v>-375.7</v>
+        <v>1502.2</v>
       </c>
       <c r="K208" t="n">
-        <v>3.302</v>
+        <v>3.3454</v>
       </c>
       <c r="L208" t="n">
-        <v>5.951</v>
+        <v>5.070138888888889</v>
       </c>
     </row>
     <row r="209">
@@ -9618,16 +9618,16 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J209" t="n">
-        <v>-751.4</v>
+        <v>-800.5</v>
       </c>
       <c r="K209" t="n">
-        <v>3.28</v>
+        <v>3.311</v>
       </c>
       <c r="L209" t="n">
-        <v>45.39533333333333</v>
+        <v>11.43786111111111</v>
       </c>
     </row>
     <row r="210">
@@ -9665,13 +9665,13 @@
         <v>5</v>
       </c>
       <c r="J210" t="n">
-        <v>-3002.2</v>
+        <v>401.7</v>
       </c>
       <c r="K210" t="n">
-        <v>3.2325</v>
+        <v>3.3147</v>
       </c>
       <c r="L210" t="n">
-        <v>23.28705555555555</v>
+        <v>1.897138888888889</v>
       </c>
     </row>
     <row r="211">
@@ -9706,16 +9706,16 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J211" t="n">
         <v>401.7</v>
       </c>
       <c r="K211" t="n">
-        <v>3.3209</v>
+        <v>3.332</v>
       </c>
       <c r="L211" t="n">
-        <v>1.897583333333333</v>
+        <v>2.343</v>
       </c>
     </row>
   </sheetData>
